--- a/lessons.xlsx
+++ b/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F2735-0EFF-48BE-8326-0ECD7233E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6B46A8-16E8-4633-A828-FD495C5486CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="165">
   <si>
     <t>Категорија</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>https://ik-cod.github.io/Matematika/data/7</t>
+  </si>
+  <si>
+    <t>Релација за еквивалентвост и подредување</t>
+  </si>
+  <si>
+    <t>https://ik-cod.github.io/Matematika/data/gemini-code-1789115761271</t>
   </si>
 </sst>
 </file>
@@ -803,7 +809,6 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
         <filter val="8"/>
       </filters>
     </filterColumn>
@@ -1116,7 +1121,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1735,7 +1740,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1752,7 +1757,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1767,7 +1772,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1797,7 +1802,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1810,7 +1815,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1823,7 +1828,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1836,7 +1841,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1849,7 +1854,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1862,7 +1867,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1875,7 +1880,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1888,7 +1893,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1901,7 +1906,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1914,7 +1919,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1927,7 +1932,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1945,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1953,7 +1958,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1966,7 +1971,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1979,7 +1984,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1992,7 +1997,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2005,7 +2010,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2018,7 +2023,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2031,7 +2036,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2044,7 +2049,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2057,7 +2062,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2070,7 +2075,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2083,7 +2088,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2096,7 +2101,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2109,7 +2114,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2127,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2135,7 +2140,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2148,7 +2153,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2161,7 +2166,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2174,7 +2179,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2187,7 +2192,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2200,7 +2205,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2213,7 +2218,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2226,7 +2231,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2239,7 +2244,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2252,7 +2257,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2318,8 +2323,12 @@
       <c r="C85" s="4">
         <v>4</v>
       </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="11"/>
+      <c r="D85" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">

--- a/lessons.xlsx
+++ b/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6B46A8-16E8-4633-A828-FD495C5486CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2BC9B5-893F-4448-8DF8-0FC59D949630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="167">
   <si>
     <t>Категорија</t>
   </si>
@@ -595,6 +595,12 @@
   </si>
   <si>
     <t>https://ik-cod.github.io/Matematika/data/gemini-code-1789115761271</t>
+  </si>
+  <si>
+    <t>Вежби за релации</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwdZK8UDUHE_5Ky4z5genO0NyB9Qn4znFhUhSgvCJf5BCFms8R6Vw4-S0GQalpnRHEN/exec</t>
   </si>
 </sst>
 </file>
@@ -2340,8 +2346,12 @@
       <c r="C86" s="4">
         <v>5</v>
       </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="11"/>
+      <c r="D86" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">

--- a/lessons.xlsx
+++ b/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2BC9B5-893F-4448-8DF8-0FC59D949630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971AE155-D015-474A-BC5C-22739282E483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     <t>Вежби за релации</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbwdZK8UDUHE_5Ky4z5genO0NyB9Qn4znFhUhSgvCJf5BCFms8R6Vw4-S0GQalpnRHEN/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbwivlQjcWhi72WQSK4uJKeXKFSecygPNRxguTqSO2WCt4s1ssSVmGlY9afFDSt9TJGk/exec</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2349,7 @@
       <c r="D86" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="13" t="s">
         <v>166</v>
       </c>
     </row>
@@ -10997,11 +10997,12 @@
   <hyperlinks>
     <hyperlink ref="E603" r:id="rId1" xr:uid="{C4BB2320-73F4-4247-B6EF-4A48501D6F90}"/>
     <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
+    <hyperlink ref="E86" r:id="rId3" xr:uid="{128E47EA-44B5-445E-9813-7B5B6E392FE6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
